--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8174DF1-6E89-46B2-8123-0D1C3AA5171A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EDFD52-CBE2-4727-9178-F75C91F87090}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1310,8 +1310,12 @@
       <c r="B23" s="31">
         <v>46067</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="37">
+        <v>354408.67</v>
+      </c>
+      <c r="D23" s="36">
+        <v>27.67</v>
+      </c>
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
       <c r="G23" s="1"/>
@@ -1768,11 +1772,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2912944</v>
+        <v>3267352.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>1297.97</v>
+        <v>1325.64</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5494,9 +5498,13 @@
       <c r="B23" s="31">
         <v>46067</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="37">
+        <v>242774</v>
+      </c>
       <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
+      <c r="E23" s="37">
+        <v>144.25</v>
+      </c>
       <c r="F23" s="36"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -5952,7 +5960,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2554726</v>
+        <v>2797500</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -5960,7 +5968,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1023.25</v>
+        <v>1167.5</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -9676,8 +9684,12 @@
       <c r="B23" s="31">
         <v>46067</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="37">
+        <v>283410</v>
+      </c>
+      <c r="D23" s="36">
+        <v>1012.25</v>
+      </c>
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
       <c r="G23" s="1"/>
@@ -10134,11 +10146,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2961461.5</v>
+        <v>3244871.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>1812.5</v>
+        <v>2824.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EDFD52-CBE2-4727-9178-F75C91F87090}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD0AD25-EA59-4C14-AC2A-6DBB51F1A557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1362,9 +1362,13 @@
       <c r="B25" s="31">
         <v>46069</v>
       </c>
-      <c r="C25" s="12"/>
+      <c r="C25" s="12">
+        <v>324575</v>
+      </c>
       <c r="D25" s="15"/>
-      <c r="E25" s="12"/>
+      <c r="E25" s="12">
+        <v>656</v>
+      </c>
       <c r="F25" s="11"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1772,7 +1776,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3267352.67</v>
+        <v>3591927.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -1780,7 +1784,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>6</v>
+        <v>662</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -5550,8 +5554,12 @@
       <c r="B25" s="31">
         <v>46069</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="15"/>
+      <c r="C25" s="12">
+        <v>341726</v>
+      </c>
+      <c r="D25" s="15">
+        <v>417.5</v>
+      </c>
       <c r="E25" s="12"/>
       <c r="F25" s="11"/>
       <c r="G25" s="1"/>
@@ -5960,11 +5968,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>2797500</v>
+        <v>3139226</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>1122.25</v>
+        <v>1539.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -9736,9 +9744,13 @@
       <c r="B25" s="31">
         <v>46069</v>
       </c>
-      <c r="C25" s="12"/>
+      <c r="C25" s="12">
+        <v>269624</v>
+      </c>
       <c r="D25" s="15"/>
-      <c r="E25" s="12"/>
+      <c r="E25" s="12">
+        <v>109.75</v>
+      </c>
       <c r="F25" s="11"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -10146,7 +10158,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3244871.5</v>
+        <v>3514495.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10154,7 +10166,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1770.25</v>
+        <v>1880</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD0AD25-EA59-4C14-AC2A-6DBB51F1A557}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961C25A8-6506-49CB-AE73-3C482BF6D9C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1389,9 +1389,13 @@
       <c r="B26" s="31">
         <v>46070</v>
       </c>
-      <c r="C26" s="12"/>
+      <c r="C26" s="12">
+        <v>256495</v>
+      </c>
       <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
+      <c r="E26" s="37">
+        <v>25</v>
+      </c>
       <c r="F26" s="11"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1776,7 +1780,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3591927.67</v>
+        <v>3848422.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -1784,7 +1788,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -5581,8 +5585,12 @@
       <c r="B26" s="31">
         <v>46070</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="36"/>
+      <c r="C26" s="12">
+        <v>245825</v>
+      </c>
+      <c r="D26" s="36">
+        <v>921.5</v>
+      </c>
       <c r="E26" s="37"/>
       <c r="F26" s="11"/>
       <c r="G26" s="1"/>
@@ -5968,11 +5976,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3139226</v>
+        <v>3385051</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>1539.75</v>
+        <v>2461.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -9771,9 +9779,13 @@
       <c r="B26" s="31">
         <v>46070</v>
       </c>
-      <c r="C26" s="12"/>
+      <c r="C26" s="12">
+        <v>339942</v>
+      </c>
       <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
+      <c r="E26" s="37">
+        <v>55.75</v>
+      </c>
       <c r="F26" s="11"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -10158,7 +10170,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3514495.5</v>
+        <v>3854437.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10166,7 +10178,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1880</v>
+        <v>1935.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961C25A8-6506-49CB-AE73-3C482BF6D9C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE77C0A-95B2-42FB-81AC-787AD0D5A941}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -1416,10 +1416,12 @@
       <c r="B27" s="31">
         <v>46071</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
+      <c r="C27" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="7"/>
@@ -4947,13 +4949,14 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -5612,9 +5615,13 @@
       <c r="B27" s="31">
         <v>46071</v>
       </c>
-      <c r="C27" s="36"/>
+      <c r="C27" s="37">
+        <v>245809</v>
+      </c>
       <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
+      <c r="E27" s="37">
+        <v>121.25</v>
+      </c>
       <c r="F27" s="36"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -5976,7 +5983,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3385051</v>
+        <v>3630860</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -5984,7 +5991,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1167.5</v>
+        <v>1288.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -9806,9 +9813,13 @@
       <c r="B27" s="31">
         <v>46071</v>
       </c>
-      <c r="C27" s="36"/>
+      <c r="C27" s="37">
+        <v>263794</v>
+      </c>
       <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
+      <c r="E27" s="37">
+        <v>4</v>
+      </c>
       <c r="F27" s="36"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -10170,7 +10181,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3854437.5</v>
+        <v>4118231.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10178,7 +10189,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1935.75</v>
+        <v>1939.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE77C0A-95B2-42FB-81AC-787AD0D5A941}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA695240-5B3F-4319-A85D-E943635D2526}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA695240-5B3F-4319-A85D-E943635D2526}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD4FB1C-A3F1-4C8F-A2BD-5BFACF201DBE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1441,8 +1441,12 @@
       <c r="B28" s="31">
         <v>46072</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="12">
+        <v>300926</v>
+      </c>
+      <c r="D28" s="13">
+        <v>1086.25</v>
+      </c>
       <c r="E28" s="12"/>
       <c r="F28" s="35"/>
       <c r="G28" s="1"/>
@@ -1782,11 +1786,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3848422.67</v>
+        <v>4149348.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>1325.64</v>
+        <v>2411.8900000000003</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5642,9 +5646,13 @@
       <c r="B28" s="31">
         <v>46072</v>
       </c>
-      <c r="C28" s="12"/>
+      <c r="C28" s="12">
+        <v>243579.67</v>
+      </c>
       <c r="D28" s="13"/>
-      <c r="E28" s="12"/>
+      <c r="E28" s="12">
+        <v>216.08</v>
+      </c>
       <c r="F28" s="35"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -5983,7 +5991,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3630860</v>
+        <v>3874439.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -5991,7 +5999,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1288.75</v>
+        <v>1504.83</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -9840,9 +9848,13 @@
       <c r="B28" s="31">
         <v>46072</v>
       </c>
-      <c r="C28" s="12"/>
+      <c r="C28" s="12">
+        <v>268991</v>
+      </c>
       <c r="D28" s="13"/>
-      <c r="E28" s="12"/>
+      <c r="E28" s="12">
+        <v>846</v>
+      </c>
       <c r="F28" s="35"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -10181,7 +10193,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4118231.5</v>
+        <v>4387222.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10189,7 +10201,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1939.75</v>
+        <v>2785.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD4FB1C-A3F1-4C8F-A2BD-5BFACF201DBE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4FFA2B-EECC-4062-BC0C-7C2E9D8F5FEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1468,8 +1468,12 @@
       <c r="B29" s="31">
         <v>46073</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="15"/>
+      <c r="C29" s="12">
+        <v>341516</v>
+      </c>
+      <c r="D29" s="15">
+        <v>604.75</v>
+      </c>
       <c r="E29" s="12"/>
       <c r="F29" s="34"/>
       <c r="G29" s="1"/>
@@ -1786,11 +1790,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4149348.67</v>
+        <v>4490864.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>2411.8900000000003</v>
+        <v>3016.6400000000003</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5673,9 +5677,13 @@
       <c r="B29" s="31">
         <v>46073</v>
       </c>
-      <c r="C29" s="27"/>
+      <c r="C29" s="12">
+        <v>148182</v>
+      </c>
       <c r="D29" s="15"/>
-      <c r="E29" s="12"/>
+      <c r="E29" s="12">
+        <v>22.25</v>
+      </c>
       <c r="F29" s="34"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -5991,7 +5999,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>3874439.67</v>
+        <v>4022621.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -5999,7 +6007,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1504.83</v>
+        <v>1527.08</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -9875,9 +9883,13 @@
       <c r="B29" s="31">
         <v>46073</v>
       </c>
-      <c r="C29" s="27"/>
+      <c r="C29" s="12">
+        <v>375047</v>
+      </c>
       <c r="D29" s="15"/>
-      <c r="E29" s="12"/>
+      <c r="E29" s="12">
+        <v>185.25</v>
+      </c>
       <c r="F29" s="34"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -10193,7 +10205,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4387222.5</v>
+        <v>4762269.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10201,7 +10213,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>2785.75</v>
+        <v>2971</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4FFA2B-EECC-4062-BC0C-7C2E9D8F5FEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF7C53B-D0A3-4ED8-9301-4E1564288CE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1495,9 +1495,13 @@
       <c r="B30" s="31">
         <v>46074</v>
       </c>
-      <c r="C30" s="36"/>
+      <c r="C30" s="37">
+        <v>329826</v>
+      </c>
       <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
+      <c r="E30" s="37">
+        <v>229.25</v>
+      </c>
       <c r="F30" s="36"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -1790,7 +1794,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4490864.67</v>
+        <v>4820690.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -1798,7 +1802,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>687</v>
+        <v>916.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -5704,9 +5708,13 @@
       <c r="B30" s="31">
         <v>46074</v>
       </c>
-      <c r="C30" s="36"/>
+      <c r="C30" s="37">
+        <v>274902</v>
+      </c>
       <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
+      <c r="E30" s="37">
+        <v>91.5</v>
+      </c>
       <c r="F30" s="36"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -5999,7 +6007,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4022621.67</v>
+        <v>4297523.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -6007,7 +6015,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1527.08</v>
+        <v>1618.58</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -9910,9 +9918,13 @@
       <c r="B30" s="31">
         <v>46074</v>
       </c>
-      <c r="C30" s="36"/>
+      <c r="C30" s="37">
+        <v>321122</v>
+      </c>
       <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
+      <c r="E30" s="37">
+        <v>2609.75</v>
+      </c>
       <c r="F30" s="36"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -10205,7 +10217,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4762269.5</v>
+        <v>5083391.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10213,7 +10225,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>2971</v>
+        <v>5580.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF7C53B-D0A3-4ED8-9301-4E1564288CE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCCEA40-371B-485C-A71A-964377FD9373}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -1547,10 +1547,12 @@
       <c r="B32" s="31">
         <v>46076</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="11"/>
+      <c r="C32" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="7"/>
@@ -4961,7 +4963,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C17:F17"/>
@@ -4969,6 +4971,7 @@
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -5760,10 +5763,12 @@
       <c r="B32" s="31">
         <v>46076</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="11"/>
+      <c r="C32" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="7"/>
@@ -9174,13 +9179,14 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="D22:E22"/>
+    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -9970,9 +9976,13 @@
       <c r="B32" s="31">
         <v>46076</v>
       </c>
-      <c r="C32" s="12"/>
+      <c r="C32" s="12">
+        <v>390982</v>
+      </c>
       <c r="D32" s="15"/>
-      <c r="E32" s="12"/>
+      <c r="E32" s="12">
+        <v>1921.5</v>
+      </c>
       <c r="F32" s="11"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -10217,7 +10227,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5083391.5</v>
+        <v>5474373.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10225,7 +10235,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>5580.75</v>
+        <v>7502.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCCEA40-371B-485C-A71A-964377FD9373}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C603B1D1-7817-497E-83E1-F5561D0276F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -38,8 +38,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="C33" authorId="0" shapeId="0" xr:uid="{0A564BDE-5738-437C-8B2A-D9F53A458F54}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+DSP: GRACE B. GICA</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -142,7 +176,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +275,19 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -767,7 +814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
   <dimension ref="A1:Q279"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1572,8 +1619,12 @@
       <c r="B33" s="31">
         <v>46077</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="36"/>
+      <c r="C33" s="12">
+        <v>283160</v>
+      </c>
+      <c r="D33" s="36">
+        <v>475</v>
+      </c>
       <c r="E33" s="35"/>
       <c r="F33" s="11"/>
       <c r="G33" s="1"/>
@@ -1796,11 +1847,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4820690.67</v>
+        <v>5103850.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>3016.6400000000003</v>
+        <v>3491.6400000000003</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -4975,6 +5026,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5788,8 +5840,12 @@
       <c r="B33" s="31">
         <v>46077</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="36"/>
+      <c r="C33" s="12">
+        <v>455067</v>
+      </c>
+      <c r="D33" s="36">
+        <v>13525.5</v>
+      </c>
       <c r="E33" s="35"/>
       <c r="F33" s="11"/>
       <c r="G33" s="1"/>
@@ -6012,11 +6068,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4297523.67</v>
+        <v>4752590.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>2461.25</v>
+        <v>15986.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10003,10 +10059,12 @@
       <c r="B33" s="31">
         <v>46077</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="11"/>
+      <c r="C33" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="41"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="7"/>
@@ -13394,13 +13452,14 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C603B1D1-7817-497E-83E1-F5561D0276F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B202DF-7940-4201-AB61-9C289E9EE6B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1646,8 +1646,12 @@
       <c r="B34" s="31">
         <v>46078</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
+      <c r="C34" s="37">
+        <v>400621</v>
+      </c>
+      <c r="D34" s="36">
+        <v>433.5</v>
+      </c>
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
       <c r="G34" s="1"/>
@@ -1847,11 +1851,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5103850.67</v>
+        <v>5504471.6699999999</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>3491.6400000000003</v>
+        <v>3925.1400000000003</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5867,9 +5871,13 @@
       <c r="B34" s="31">
         <v>46078</v>
       </c>
-      <c r="C34" s="36"/>
+      <c r="C34" s="37">
+        <v>211051</v>
+      </c>
       <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
+      <c r="E34" s="37">
+        <v>691</v>
+      </c>
       <c r="F34" s="36"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -6068,7 +6076,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4752590.67</v>
+        <v>4963641.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -6076,7 +6084,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>1618.58</v>
+        <v>2309.58</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -10084,8 +10092,12 @@
       <c r="B34" s="31">
         <v>46078</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
+      <c r="C34" s="37">
+        <v>320829</v>
+      </c>
+      <c r="D34" s="36">
+        <v>1507.5</v>
+      </c>
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
       <c r="G34" s="1"/>
@@ -10285,11 +10297,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5474373.5</v>
+        <v>5795202.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>2824.75</v>
+        <v>4332.25</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B202DF-7940-4201-AB61-9C289E9EE6B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1121B9EB-D6AA-4526-B984-F2CACBCC452F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="FEBRUARY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1673,9 +1673,13 @@
       <c r="B35" s="31">
         <v>46079</v>
       </c>
-      <c r="C35" s="12"/>
+      <c r="C35" s="12">
+        <v>251863</v>
+      </c>
       <c r="D35" s="13"/>
-      <c r="E35" s="12"/>
+      <c r="E35" s="12">
+        <v>61</v>
+      </c>
       <c r="F35" s="35"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1851,7 +1855,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5504471.6699999999</v>
+        <v>5756334.6699999999</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>916.25</v>
+        <v>977.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -5898,8 +5902,12 @@
       <c r="B35" s="31">
         <v>46079</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="12">
+        <v>239830</v>
+      </c>
+      <c r="D35" s="13">
+        <v>210.75</v>
+      </c>
       <c r="E35" s="12"/>
       <c r="F35" s="35"/>
       <c r="G35" s="1"/>
@@ -6076,11 +6084,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>4963641.67</v>
+        <v>5203471.67</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>15986.75</v>
+        <v>16197.5</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10119,8 +10127,12 @@
       <c r="B35" s="31">
         <v>46079</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
+      <c r="C35" s="12">
+        <v>239654</v>
+      </c>
+      <c r="D35" s="13">
+        <v>2106.5</v>
+      </c>
       <c r="E35" s="12"/>
       <c r="F35" s="35"/>
       <c r="G35" s="1"/>
@@ -10297,11 +10309,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5795202.5</v>
+        <v>6034856.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>4332.25</v>
+        <v>6438.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1121B9EB-D6AA-4526-B984-F2CACBCC452F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61D412E-5E12-4347-B6DB-DC75717175F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1700,8 +1700,12 @@
       <c r="B36" s="31">
         <v>46080</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="12">
+        <v>320471</v>
+      </c>
+      <c r="D36" s="13">
+        <v>193</v>
+      </c>
       <c r="E36" s="12"/>
       <c r="F36" s="35"/>
       <c r="G36" s="1"/>
@@ -1855,11 +1859,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5756334.6699999999</v>
+        <v>6076805.6699999999</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>3925.1400000000003</v>
+        <v>4118.1400000000003</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -5929,8 +5933,12 @@
       <c r="B36" s="31">
         <v>46080</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
+      <c r="C36" s="12">
+        <v>217575</v>
+      </c>
+      <c r="D36" s="13">
+        <v>201.5</v>
+      </c>
       <c r="E36" s="12"/>
       <c r="F36" s="35"/>
       <c r="G36" s="1"/>
@@ -6084,11 +6092,11 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>5203471.67</v>
+        <v>5421046.6699999999</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
-        <v>16197.5</v>
+        <v>16399</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -10154,9 +10162,13 @@
       <c r="B36" s="31">
         <v>46080</v>
       </c>
-      <c r="C36" s="12"/>
+      <c r="C36" s="12">
+        <v>235375</v>
+      </c>
       <c r="D36" s="13"/>
-      <c r="E36" s="12"/>
+      <c r="E36" s="12">
+        <v>70</v>
+      </c>
       <c r="F36" s="35"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -10309,7 +10321,7 @@
       <c r="B43" s="31"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6034856.5</v>
+        <v>6270231.5</v>
       </c>
       <c r="D43" s="32">
         <f>SUM(D10:D42)</f>
@@ -10317,7 +10329,7 @@
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>7502.25</v>
+        <v>7572.25</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>

--- a/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/SHORT OVER ALL ROUTES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61D412E-5E12-4347-B6DB-DC75717175F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85AAB07-1ABE-4BB7-BAAA-92AB675BB476}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="18">
   <si>
     <t>SALES</t>
   </si>
@@ -398,7 +398,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -438,9 +438,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1009,15 +1006,15 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="41"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1034,16 +1031,16 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>46055</v>
       </c>
       <c r="C11" s="12">
         <v>314042</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="35">
         <v>170</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="11"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1061,7 +1058,7 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46056</v>
       </c>
       <c r="C12" s="12">
@@ -1088,17 +1085,17 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>46057</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="36">
         <v>198091</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>19.25</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1115,7 +1112,7 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46058</v>
       </c>
       <c r="C14" s="12">
@@ -1125,7 +1122,7 @@
         <v>320</v>
       </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="36"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1142,7 +1139,7 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>46059</v>
       </c>
       <c r="C15" s="12">
@@ -1152,7 +1149,7 @@
         <v>115.5</v>
       </c>
       <c r="E15" s="12"/>
-      <c r="F15" s="34"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1169,17 +1166,17 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46060</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>173376</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="35">
         <v>25.75</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1196,15 +1193,15 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1221,7 +1218,7 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46062</v>
       </c>
       <c r="C18" s="12">
@@ -1248,16 +1245,16 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>46063</v>
       </c>
       <c r="C19" s="12">
         <v>197103</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="35">
         <v>123.72</v>
       </c>
-      <c r="E19" s="38"/>
+      <c r="E19" s="37"/>
       <c r="F19" s="11"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1275,17 +1272,17 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46064</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="36">
         <v>809196</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="35">
         <v>226</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1302,7 +1299,7 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>46065</v>
       </c>
       <c r="C21" s="12">
@@ -1312,7 +1309,7 @@
         <v>76.5</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1329,15 +1326,15 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46066</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="41"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1354,17 +1351,17 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="30">
         <v>46067</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="36">
         <v>354408.67</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="35">
         <v>27.67</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="7"/>
@@ -1381,15 +1378,15 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="7"/>
@@ -1406,7 +1403,7 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>46069</v>
       </c>
       <c r="C25" s="12">
@@ -1433,14 +1430,14 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46070</v>
       </c>
       <c r="C26" s="12">
         <v>256495</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37">
+      <c r="D26" s="35"/>
+      <c r="E26" s="36">
         <v>25</v>
       </c>
       <c r="F26" s="11"/>
@@ -1460,15 +1457,15 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>46071</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="41"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="7"/>
@@ -1485,7 +1482,7 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46072</v>
       </c>
       <c r="C28" s="12">
@@ -1495,7 +1492,7 @@
         <v>1086.25</v>
       </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="35"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="7"/>
@@ -1512,7 +1509,7 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>46073</v>
       </c>
       <c r="C29" s="12">
@@ -1522,7 +1519,7 @@
         <v>604.75</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="34"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="7"/>
@@ -1539,17 +1536,17 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46074</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="36">
         <v>329826</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37">
+      <c r="D30" s="35"/>
+      <c r="E30" s="36">
         <v>229.25</v>
       </c>
-      <c r="F30" s="36"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="7"/>
@@ -1566,15 +1563,15 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="41"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="19"/>
@@ -1591,15 +1588,15 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46076</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="41"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="7"/>
@@ -1616,16 +1613,16 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="30">
         <v>46077</v>
       </c>
       <c r="C33" s="12">
         <v>283160</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="35">
         <v>475</v>
       </c>
-      <c r="E33" s="35"/>
+      <c r="E33" s="34"/>
       <c r="F33" s="11"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -1643,17 +1640,17 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46078</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="36">
         <v>400621</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="35">
         <v>433.5</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="7"/>
@@ -1670,7 +1667,7 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>46079</v>
       </c>
       <c r="C35" s="12">
@@ -1680,7 +1677,7 @@
       <c r="E35" s="12">
         <v>61</v>
       </c>
-      <c r="F35" s="35"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="7"/>
@@ -1697,7 +1694,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46080</v>
       </c>
       <c r="C36" s="12">
@@ -1707,7 +1704,7 @@
         <v>193</v>
       </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="35"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="7"/>
@@ -1724,13 +1721,17 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>46081</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="15"/>
+      <c r="C37" s="12">
+        <v>529984</v>
+      </c>
+      <c r="D37" s="15">
+        <v>85.5</v>
+      </c>
       <c r="E37" s="12"/>
-      <c r="F37" s="34"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="8"/>
@@ -1747,15 +1748,15 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="7"/>
@@ -1772,7 +1773,7 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="31"/>
+      <c r="B39" s="30"/>
       <c r="C39" s="12"/>
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
@@ -1793,7 +1794,7 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="31"/>
+      <c r="B40" s="30"/>
       <c r="C40" s="12"/>
       <c r="D40" s="15"/>
       <c r="E40" s="12"/>
@@ -1814,10 +1815,10 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
       <c r="F41" s="11"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -1835,7 +1836,7 @@
       <c r="A42" s="24">
         <v>31</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -1853,17 +1854,17 @@
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:17" ht="15">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6076805.6699999999</v>
-      </c>
-      <c r="D43" s="32">
+        <v>6606789.6699999999</v>
+      </c>
+      <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
-        <v>4118.1400000000003</v>
+        <v>4203.6400000000003</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
@@ -1887,9 +1888,9 @@
     </row>
     <row r="44" spans="1:17" ht="15">
       <c r="A44" s="22"/>
-      <c r="B44" s="33"/>
+      <c r="B44" s="32"/>
       <c r="C44" s="23"/>
-      <c r="D44" s="28"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="9"/>
       <c r="F44" s="22"/>
       <c r="G44" s="1"/>
@@ -5238,15 +5239,15 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="41"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -5263,14 +5264,14 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>46055</v>
       </c>
       <c r="C11" s="12">
         <v>403660</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="38">
+      <c r="D11" s="35"/>
+      <c r="E11" s="37">
         <v>112.75</v>
       </c>
       <c r="F11" s="11"/>
@@ -5290,7 +5291,7 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46056</v>
       </c>
       <c r="C12" s="12">
@@ -5317,17 +5318,17 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>46057</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="36">
         <v>176482</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37">
+      <c r="D13" s="35"/>
+      <c r="E13" s="36">
         <v>215.25</v>
       </c>
-      <c r="F13" s="36"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -5344,7 +5345,7 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46058</v>
       </c>
       <c r="C14" s="12">
@@ -5354,7 +5355,7 @@
       <c r="E14" s="12">
         <v>311</v>
       </c>
-      <c r="F14" s="36"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -5371,7 +5372,7 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>46059</v>
       </c>
       <c r="C15" s="12">
@@ -5381,7 +5382,7 @@
       <c r="E15" s="12">
         <v>0.75</v>
       </c>
-      <c r="F15" s="34"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -5398,17 +5399,17 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46060</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>267745</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="35">
         <v>31.5</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5425,15 +5426,15 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5450,7 +5451,7 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46062</v>
       </c>
       <c r="C18" s="12">
@@ -5477,16 +5478,16 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>46063</v>
       </c>
       <c r="C19" s="12">
         <v>205618</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="35">
         <v>564.75</v>
       </c>
-      <c r="E19" s="38"/>
+      <c r="E19" s="37"/>
       <c r="F19" s="11"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -5504,17 +5505,17 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46064</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="36">
         <v>170729</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="35">
         <v>50.5</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5531,7 +5532,7 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>46065</v>
       </c>
       <c r="C21" s="12">
@@ -5541,7 +5542,7 @@
         <v>370</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5558,17 +5559,17 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46066</v>
       </c>
       <c r="C22" s="12">
         <v>163881</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="34"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5585,17 +5586,17 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="30">
         <v>46067</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="36">
         <v>242774</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37">
+      <c r="D23" s="35"/>
+      <c r="E23" s="36">
         <v>144.25</v>
       </c>
-      <c r="F23" s="36"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="7"/>
@@ -5612,15 +5613,15 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="7"/>
@@ -5637,7 +5638,7 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>46069</v>
       </c>
       <c r="C25" s="12">
@@ -5664,16 +5665,16 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46070</v>
       </c>
       <c r="C26" s="12">
         <v>245825</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="35">
         <v>921.5</v>
       </c>
-      <c r="E26" s="37"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="11"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -5691,17 +5692,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>46071</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="36">
         <v>245809</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37">
+      <c r="D27" s="35"/>
+      <c r="E27" s="36">
         <v>121.25</v>
       </c>
-      <c r="F27" s="36"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="7"/>
@@ -5718,7 +5719,7 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46072</v>
       </c>
       <c r="C28" s="12">
@@ -5728,7 +5729,7 @@
       <c r="E28" s="12">
         <v>216.08</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="7"/>
@@ -5745,7 +5746,7 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>46073</v>
       </c>
       <c r="C29" s="12">
@@ -5755,7 +5756,7 @@
       <c r="E29" s="12">
         <v>22.25</v>
       </c>
-      <c r="F29" s="34"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="7"/>
@@ -5772,17 +5773,17 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46074</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="36">
         <v>274902</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37">
+      <c r="D30" s="35"/>
+      <c r="E30" s="36">
         <v>91.5</v>
       </c>
-      <c r="F30" s="36"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="7"/>
@@ -5799,15 +5800,15 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="41"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="19"/>
@@ -5824,15 +5825,15 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46076</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="41"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="7"/>
@@ -5849,16 +5850,16 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="30">
         <v>46077</v>
       </c>
       <c r="C33" s="12">
         <v>455067</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="35">
         <v>13525.5</v>
       </c>
-      <c r="E33" s="35"/>
+      <c r="E33" s="34"/>
       <c r="F33" s="11"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -5876,17 +5877,17 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46078</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="36">
         <v>211051</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="37">
+      <c r="D34" s="35"/>
+      <c r="E34" s="36">
         <v>691</v>
       </c>
-      <c r="F34" s="36"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="7"/>
@@ -5903,7 +5904,7 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>46079</v>
       </c>
       <c r="C35" s="12">
@@ -5913,7 +5914,7 @@
         <v>210.75</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="35"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="7"/>
@@ -5930,7 +5931,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46080</v>
       </c>
       <c r="C36" s="12">
@@ -5940,7 +5941,7 @@
         <v>201.5</v>
       </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="35"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="7"/>
@@ -5957,13 +5958,15 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>46081</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="34"/>
+      <c r="C37" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="8"/>
@@ -5980,15 +5983,15 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="7"/>
@@ -6005,7 +6008,7 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="31"/>
+      <c r="B39" s="30"/>
       <c r="C39" s="12"/>
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
@@ -6026,7 +6029,7 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="31"/>
+      <c r="B40" s="30"/>
       <c r="C40" s="12"/>
       <c r="D40" s="15"/>
       <c r="E40" s="12"/>
@@ -6047,10 +6050,10 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
       <c r="F41" s="11"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -6068,7 +6071,7 @@
       <c r="A42" s="24">
         <v>31</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -6086,15 +6089,15 @@
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:17" ht="15">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
         <v>5421046.6699999999</v>
       </c>
-      <c r="D43" s="32">
+      <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
         <v>16399</v>
       </c>
@@ -6122,7 +6125,7 @@
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="23"/>
-      <c r="D44" s="28"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="9"/>
       <c r="F44" s="22"/>
       <c r="G44" s="1"/>
@@ -9259,7 +9262,7 @@
       <c r="E279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C17:F17"/>
@@ -9267,6 +9270,7 @@
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -9469,15 +9473,15 @@
       <c r="A10" s="11">
         <v>1</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="41"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -9494,14 +9498,14 @@
       <c r="A11" s="11">
         <v>2</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>46055</v>
       </c>
       <c r="C11" s="12">
         <v>293070</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="38">
+      <c r="D11" s="35"/>
+      <c r="E11" s="37">
         <v>1008.5</v>
       </c>
       <c r="F11" s="11"/>
@@ -9521,7 +9525,7 @@
       <c r="A12" s="11">
         <v>3</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46056</v>
       </c>
       <c r="C12" s="12">
@@ -9548,17 +9552,17 @@
       <c r="A13" s="11">
         <v>4</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>46057</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="36">
         <v>505520</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>636.25</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -9575,7 +9579,7 @@
       <c r="A14" s="11">
         <v>5</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46058</v>
       </c>
       <c r="C14" s="12">
@@ -9585,7 +9589,7 @@
       <c r="E14" s="12">
         <v>37.5</v>
       </c>
-      <c r="F14" s="36"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -9602,15 +9606,15 @@
       <c r="A15" s="11">
         <v>6</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>46059</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="41"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -9627,17 +9631,17 @@
       <c r="A16" s="11">
         <v>7</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46060</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="36">
         <v>294192</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="35">
         <v>73.5</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -9654,15 +9658,15 @@
       <c r="A17" s="11">
         <v>8</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -9679,7 +9683,7 @@
       <c r="A18" s="11">
         <v>9</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46062</v>
       </c>
       <c r="C18" s="12">
@@ -9706,14 +9710,14 @@
       <c r="A19" s="11">
         <v>10</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>46063</v>
       </c>
       <c r="C19" s="12">
         <v>317068</v>
       </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="38">
+      <c r="D19" s="35"/>
+      <c r="E19" s="37">
         <v>118</v>
       </c>
       <c r="F19" s="11"/>
@@ -9733,17 +9737,17 @@
       <c r="A20" s="11">
         <v>11</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46064</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="36">
         <v>295569</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="35">
         <v>552.5</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9760,7 +9764,7 @@
       <c r="A21" s="11">
         <v>12</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>46065</v>
       </c>
       <c r="C21" s="12">
@@ -9770,7 +9774,7 @@
       <c r="E21" s="12">
         <v>505.25</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -9787,7 +9791,7 @@
       <c r="A22" s="11">
         <v>13</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46066</v>
       </c>
       <c r="C22" s="12">
@@ -9797,7 +9801,7 @@
         <v>71.25</v>
       </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="34"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -9814,17 +9818,17 @@
       <c r="A23" s="11">
         <v>14</v>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="30">
         <v>46067</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="36">
         <v>283410</v>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="35">
         <v>1012.25</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="7"/>
@@ -9841,15 +9845,15 @@
       <c r="A24" s="11">
         <v>15</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="7"/>
@@ -9866,7 +9870,7 @@
       <c r="A25" s="11">
         <v>16</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>46069</v>
       </c>
       <c r="C25" s="12">
@@ -9893,14 +9897,14 @@
       <c r="A26" s="11">
         <v>17</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46070</v>
       </c>
       <c r="C26" s="12">
         <v>339942</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37">
+      <c r="D26" s="35"/>
+      <c r="E26" s="36">
         <v>55.75</v>
       </c>
       <c r="F26" s="11"/>
@@ -9920,17 +9924,17 @@
       <c r="A27" s="11">
         <v>18</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>46071</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="36">
         <v>263794</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37">
+      <c r="D27" s="35"/>
+      <c r="E27" s="36">
         <v>4</v>
       </c>
-      <c r="F27" s="36"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="7"/>
@@ -9947,7 +9951,7 @@
       <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46072</v>
       </c>
       <c r="C28" s="12">
@@ -9957,7 +9961,7 @@
       <c r="E28" s="12">
         <v>846</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="7"/>
@@ -9974,7 +9978,7 @@
       <c r="A29" s="11">
         <v>20</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>46073</v>
       </c>
       <c r="C29" s="12">
@@ -9984,7 +9988,7 @@
       <c r="E29" s="12">
         <v>185.25</v>
       </c>
-      <c r="F29" s="34"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="7"/>
@@ -10001,17 +10005,17 @@
       <c r="A30" s="11">
         <v>21</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46074</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="36">
         <v>321122</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37">
+      <c r="D30" s="35"/>
+      <c r="E30" s="36">
         <v>2609.75</v>
       </c>
-      <c r="F30" s="36"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="7"/>
@@ -10028,15 +10032,15 @@
       <c r="A31" s="11">
         <v>22</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="41"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="19"/>
@@ -10053,7 +10057,7 @@
       <c r="A32" s="11">
         <v>23</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46076</v>
       </c>
       <c r="C32" s="12">
@@ -10080,15 +10084,15 @@
       <c r="A33" s="11">
         <v>24</v>
       </c>
-      <c r="B33" s="31">
+      <c r="B33" s="30">
         <v>46077</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="41"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="40"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="7"/>
@@ -10105,17 +10109,17 @@
       <c r="A34" s="11">
         <v>25</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46078</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="36">
         <v>320829</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="35">
         <v>1507.5</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="7"/>
@@ -10132,7 +10136,7 @@
       <c r="A35" s="11">
         <v>26</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>46079</v>
       </c>
       <c r="C35" s="12">
@@ -10142,7 +10146,7 @@
         <v>2106.5</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="35"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="7"/>
@@ -10159,7 +10163,7 @@
       <c r="A36" s="11">
         <v>27</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46080</v>
       </c>
       <c r="C36" s="12">
@@ -10169,7 +10173,7 @@
       <c r="E36" s="12">
         <v>70</v>
       </c>
-      <c r="F36" s="35"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="7"/>
@@ -10186,13 +10190,17 @@
       <c r="A37" s="11">
         <v>28</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>46081</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="12">
+        <v>332499</v>
+      </c>
       <c r="D37" s="15"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="34"/>
+      <c r="E37" s="12">
+        <v>876.5</v>
+      </c>
+      <c r="F37" s="33"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="8"/>
@@ -10209,15 +10217,15 @@
       <c r="A38" s="11">
         <v>29</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="7"/>
@@ -10234,7 +10242,7 @@
       <c r="A39" s="11">
         <v>30</v>
       </c>
-      <c r="B39" s="31"/>
+      <c r="B39" s="30"/>
       <c r="C39" s="12"/>
       <c r="D39" s="13"/>
       <c r="E39" s="12"/>
@@ -10255,7 +10263,7 @@
       <c r="A40" s="11">
         <v>29</v>
       </c>
-      <c r="B40" s="31"/>
+      <c r="B40" s="30"/>
       <c r="C40" s="12"/>
       <c r="D40" s="15"/>
       <c r="E40" s="12"/>
@@ -10276,10 +10284,10 @@
       <c r="A41" s="11">
         <v>30</v>
       </c>
-      <c r="B41" s="30"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="12"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
       <c r="F41" s="11"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -10297,7 +10305,7 @@
       <c r="A42" s="24">
         <v>31</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="12"/>
       <c r="D42" s="13"/>
       <c r="E42" s="12"/>
@@ -10315,21 +10323,21 @@
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:17" ht="15">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="18">
         <f>SUM(C10:C42)</f>
-        <v>6270231.5</v>
-      </c>
-      <c r="D43" s="32">
+        <v>6602730.5</v>
+      </c>
+      <c r="D43" s="31">
         <f>SUM(D10:D42)</f>
         <v>6438.75</v>
       </c>
       <c r="E43" s="18">
         <f>SUM(E10:E42)</f>
-        <v>7572.25</v>
+        <v>8448.75</v>
       </c>
       <c r="F43" s="18">
         <f>SUM(F10:F42)</f>
@@ -10351,7 +10359,7 @@
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="23"/>
-      <c r="D44" s="28"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="9"/>
       <c r="F44" s="22"/>
       <c r="G44" s="1"/>
